--- a/reports/week1.xlsx
+++ b/reports/week1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\github\FinalProjectTemplate\reports\week1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATN_NGUYEN_CHI_THANH\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE04DF6-3D3F-4E8E-B4E9-A5FCD46E2185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A5892F-ED6E-4AA7-9F44-8F38EA15CCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="970" yWindow="-110" windowWidth="18340" windowHeight="11020" xr2:uid="{C37E5B6C-C311-4F5D-9900-A9BE8D593DB2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C37E5B6C-C311-4F5D-9900-A9BE8D593DB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Báo cáo tiến độ</t>
   </si>
@@ -63,6 +63,26 @@
   </si>
   <si>
     <t>Công việc dự kiến tuần tới</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Thành</t>
+  </si>
+  <si>
+    <t>Website: Cửa hàng tạp hóa trực tuyến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mô tả luồng hoạt động
+Thiết kế các biểu đồ UC của user và admin
+</t>
+  </si>
+  <si>
+    <t>21/09/2025</t>
+  </si>
+  <si>
+    <t>Thiết kế Database và API</t>
   </si>
 </sst>
 </file>
@@ -134,13 +154,9 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -150,6 +166,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,122 +507,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E545B4C-55FB-4176-94C7-7ECFA0834383}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" customWidth="1"/>
     <col min="2" max="2" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" ht="22.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="B6" s="7">
+        <v>191667</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
